--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -24,12 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>numero_guia</t>
-  </si>
-  <si>
-    <t>GUIA-ABC-123</t>
   </si>
 </sst>
 </file>
@@ -375,7 +372,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45697611806</v>
+        <v>45701236513</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -385,17 +382,17 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45699798530</v>
+        <v>45690629541</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>1</v>
+      <c r="A5" s="3">
+        <v>45699071106</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>45697611806</v>
+        <v>45701236513</v>
       </c>
     </row>
   </sheetData>

--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -33,18 +33,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,16 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -358,10 +347,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -371,29 +360,29 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>45701236513</v>
+      <c r="A2" s="1">
+        <v>45686165665</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>45699071106</v>
+      <c r="A3" s="1">
+        <v>45701695087</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>45690629541</v>
-      </c>
+      <c r="A4"/>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>45699071106</v>
-      </c>
+      <c r="A5"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>45701236513</v>
-      </c>
+      <c r="A6"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -24,9 +24,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>numero_guia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>AMPM8003579</t>
+  </si>
+  <si>
+    <t>AMPM8009534</t>
+  </si>
+  <si>
+    <t>958494950016</t>
+  </si>
+  <si>
+    <t>955337230010</t>
+  </si>
+  <si>
+    <t>45709834061</t>
+  </si>
+  <si>
+    <t>954478260019</t>
+  </si>
+  <si>
+    <t>45704880850</t>
   </si>
 </sst>
 </file>
@@ -42,15 +66,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,13 +94,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -347,42 +410,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>45686165665</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>45705084408</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>45701695087</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5"/>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>numero_guia</t>
   </si>
@@ -32,25 +32,46 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>AMPM8003579</t>
-  </si>
-  <si>
-    <t>AMPM8009534</t>
-  </si>
-  <si>
-    <t>958494950016</t>
-  </si>
-  <si>
-    <t>955337230010</t>
-  </si>
-  <si>
-    <t>45709834061</t>
-  </si>
-  <si>
-    <t>954478260019</t>
-  </si>
-  <si>
-    <t>45704880850</t>
+    <t>45702592202</t>
+  </si>
+  <si>
+    <t>45709736037</t>
+  </si>
+  <si>
+    <t>45709116975</t>
+  </si>
+  <si>
+    <t>45709736031</t>
+  </si>
+  <si>
+    <t>45708106099</t>
+  </si>
+  <si>
+    <t>45686654524</t>
+  </si>
+  <si>
+    <t>45686165540</t>
+  </si>
+  <si>
+    <t>45713701162</t>
+  </si>
+  <si>
+    <t>45712092109</t>
+  </si>
+  <si>
+    <t>{"ID":"45706599155","t":"lm"}</t>
+  </si>
+  <si>
+    <t>45690641525</t>
+  </si>
+  <si>
+    <t>{"id":"45707569377","t":"lm"}</t>
+  </si>
+  <si>
+    <t>45701442857</t>
+  </si>
+  <si>
+    <t>45676645942</t>
   </si>
 </sst>
 </file>
@@ -66,18 +87,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -113,21 +128,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -410,75 +419,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>45705084408</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>45701695087</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>5</v>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -24,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
-  <si>
-    <t>numero_guia</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -430,26 +427,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
+      <c r="A1" s="3">
+        <v>46702592202</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="3">
+        <v>46704880850</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
+      <c r="A5" s="5">
+        <v>45704880850</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -458,11 +457,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4">
+        <v>46701695087</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -472,25 +473,30 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45701695087</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -500,12 +506,12 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -518,9 +524,14 @@
         <v>45702592202</v>
       </c>
     </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45701695087</v>
+      </c>
+    </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -24,33 +24,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>AMPM8003579</t>
-  </si>
-  <si>
-    <t>AMPM8009534</t>
-  </si>
-  <si>
-    <t>958494950016</t>
-  </si>
-  <si>
-    <t>955337230010</t>
-  </si>
-  <si>
-    <t>45709834061</t>
-  </si>
-  <si>
-    <t>954478260019</t>
   </si>
   <si>
     <t>45704880850</t>
   </si>
   <si>
-    <t>{"ID":"45706599155","t":"lm"}</t>
+    <t>45705084408</t>
+  </si>
+  <si>
+    <t>46701695087</t>
   </si>
 </sst>
 </file>
@@ -66,33 +51,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -100,43 +67,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -419,120 +356,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3">
-        <v>46702592202</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
+        <v>45709834061</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>46704880850</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>45704880850</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>45705084408</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46701695087</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>45701695087</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>45701695087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D13" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>45709834061</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>45713591400</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>45702592202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>45701695087</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto\Pruebas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\El 498\Desktop\PYTHON\AMPMAuto\Pruebas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,26 +24,175 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>45704880850</t>
-  </si>
-  <si>
-    <t>45705084408</t>
-  </si>
-  <si>
-    <t>46701695087</t>
+    <t>47211807828</t>
+  </si>
+  <si>
+    <t>47219982378</t>
+  </si>
+  <si>
+    <t>47198179950</t>
+  </si>
+  <si>
+    <t>47207593653</t>
+  </si>
+  <si>
+    <t>47206817322</t>
+  </si>
+  <si>
+    <t>47211807852</t>
+  </si>
+  <si>
+    <t>47191718384</t>
+  </si>
+  <si>
+    <t>47212277835</t>
+  </si>
+  <si>
+    <t>47206563156</t>
+  </si>
+  <si>
+    <t>47212041827</t>
+  </si>
+  <si>
+    <t>47192686038</t>
+  </si>
+  <si>
+    <t>47197803721</t>
+  </si>
+  <si>
+    <t>47211292530</t>
+  </si>
+  <si>
+    <t>47218791855</t>
+  </si>
+  <si>
+    <t>47218656808</t>
+  </si>
+  <si>
+    <t>47215253452</t>
+  </si>
+  <si>
+    <t>47207577868</t>
+  </si>
+  <si>
+    <t>47216710911</t>
+  </si>
+  <si>
+    <t>47197080943</t>
+  </si>
+  <si>
+    <t>47218915981</t>
+  </si>
+  <si>
+    <t>47193537613</t>
+  </si>
+  <si>
+    <t>47216702068</t>
+  </si>
+  <si>
+    <t>47209335878</t>
+  </si>
+  <si>
+    <t>47168175889</t>
+  </si>
+  <si>
+    <t>47192440663</t>
+  </si>
+  <si>
+    <t>47212460228</t>
+  </si>
+  <si>
+    <t>47217422003</t>
+  </si>
+  <si>
+    <t>47216382695</t>
+  </si>
+  <si>
+    <t>47217814220</t>
+  </si>
+  <si>
+    <t>47216337176</t>
+  </si>
+  <si>
+    <t>47218876935</t>
+  </si>
+  <si>
+    <t>47218117104</t>
+  </si>
+  <si>
+    <t>47200607128</t>
+  </si>
+  <si>
+    <t>47218506657</t>
+  </si>
+  <si>
+    <t>47211319457</t>
+  </si>
+  <si>
+    <t>47215973832</t>
+  </si>
+  <si>
+    <t>47211311510</t>
+  </si>
+  <si>
+    <t>47199825010</t>
+  </si>
+  <si>
+    <t>47199866606</t>
+  </si>
+  <si>
+    <t>47178488340</t>
+  </si>
+  <si>
+    <t>47217700591</t>
+  </si>
+  <si>
+    <t>47215576099</t>
+  </si>
+  <si>
+    <t>47218470731</t>
+  </si>
+  <si>
+    <t>47215899559</t>
+  </si>
+  <si>
+    <t>47192673308</t>
+  </si>
+  <si>
+    <t>47218001782</t>
+  </si>
+  <si>
+    <t>47212565979</t>
+  </si>
+  <si>
+    <t>47199087295</t>
+  </si>
+  <si>
+    <t>47214247679</t>
+  </si>
+  <si>
+    <t>47212041793</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -71,11 +220,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -356,73 +506,266 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>45709834061</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>46704880850</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
       <c r="B13" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16"/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pruebas/Prueba1.xlsx
+++ b/Pruebas/Prueba1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -177,6 +177,1407 @@
   </si>
   <si>
     <t>47212041793</t>
+  </si>
+  <si>
+    <t>47216724119</t>
+  </si>
+  <si>
+    <t>47212316148</t>
+  </si>
+  <si>
+    <t>47216304557</t>
+  </si>
+  <si>
+    <t>47211835505</t>
+  </si>
+  <si>
+    <t>47220076151</t>
+  </si>
+  <si>
+    <t>47176932388</t>
+  </si>
+  <si>
+    <t>47210951836</t>
+  </si>
+  <si>
+    <t>47197603027</t>
+  </si>
+  <si>
+    <t>47209061437</t>
+  </si>
+  <si>
+    <t>47190484453</t>
+  </si>
+  <si>
+    <t>47205876763</t>
+  </si>
+  <si>
+    <t>47215893520</t>
+  </si>
+  <si>
+    <t>47208458375</t>
+  </si>
+  <si>
+    <t>47211491212</t>
+  </si>
+  <si>
+    <t>47211507225</t>
+  </si>
+  <si>
+    <t>47211611186</t>
+  </si>
+  <si>
+    <t>47211762672</t>
+  </si>
+  <si>
+    <t>47211784346</t>
+  </si>
+  <si>
+    <t>47211838030</t>
+  </si>
+  <si>
+    <t>47211838086</t>
+  </si>
+  <si>
+    <t>47211879107</t>
+  </si>
+  <si>
+    <t>47211988819</t>
+  </si>
+  <si>
+    <t>47212307305</t>
+  </si>
+  <si>
+    <t>47212427184</t>
+  </si>
+  <si>
+    <t>47212512775</t>
+  </si>
+  <si>
+    <t>47212530067</t>
+  </si>
+  <si>
+    <t>47212631242</t>
+  </si>
+  <si>
+    <t>47213037945</t>
+  </si>
+  <si>
+    <t>47213216522</t>
+  </si>
+  <si>
+    <t>47213316706</t>
+  </si>
+  <si>
+    <t>47222898180</t>
+  </si>
+  <si>
+    <t>47222833143</t>
+  </si>
+  <si>
+    <t>47222792506</t>
+  </si>
+  <si>
+    <t>47222775020</t>
+  </si>
+  <si>
+    <t>47222739467</t>
+  </si>
+  <si>
+    <t>47222676087</t>
+  </si>
+  <si>
+    <t>47222623795</t>
+  </si>
+  <si>
+    <t>47222623759</t>
+  </si>
+  <si>
+    <t>47222584384</t>
+  </si>
+  <si>
+    <t>47222481854</t>
+  </si>
+  <si>
+    <t>47222248901</t>
+  </si>
+  <si>
+    <t>47222171781</t>
+  </si>
+  <si>
+    <t>47222171755</t>
+  </si>
+  <si>
+    <t>47222154193</t>
+  </si>
+  <si>
+    <t>47222052035</t>
+  </si>
+  <si>
+    <t>47221998221</t>
+  </si>
+  <si>
+    <t>47221997115</t>
+  </si>
+  <si>
+    <t>47221837635</t>
+  </si>
+  <si>
+    <t>47221632529</t>
+  </si>
+  <si>
+    <t>47221287915</t>
+  </si>
+  <si>
+    <t>47221151696</t>
+  </si>
+  <si>
+    <t>47221025128</t>
+  </si>
+  <si>
+    <t>47221005322</t>
+  </si>
+  <si>
+    <t>47220986612</t>
+  </si>
+  <si>
+    <t>47220986602</t>
+  </si>
+  <si>
+    <t>47220981586</t>
+  </si>
+  <si>
+    <t>47220960168</t>
+  </si>
+  <si>
+    <t>47220939628</t>
+  </si>
+  <si>
+    <t>47220932471</t>
+  </si>
+  <si>
+    <t>47220929156</t>
+  </si>
+  <si>
+    <t>47220917089</t>
+  </si>
+  <si>
+    <t>47220912759</t>
+  </si>
+  <si>
+    <t>47214773682</t>
+  </si>
+  <si>
+    <t>47215220448</t>
+  </si>
+  <si>
+    <t>47215227896</t>
+  </si>
+  <si>
+    <t>47215363968</t>
+  </si>
+  <si>
+    <t>47215494970</t>
+  </si>
+  <si>
+    <t>47215495084</t>
+  </si>
+  <si>
+    <t>47215598460</t>
+  </si>
+  <si>
+    <t>47215786701</t>
+  </si>
+  <si>
+    <t>47215798824</t>
+  </si>
+  <si>
+    <t>47215842097</t>
+  </si>
+  <si>
+    <t>47215966706</t>
+  </si>
+  <si>
+    <t>47215966996</t>
+  </si>
+  <si>
+    <t>47216095419</t>
+  </si>
+  <si>
+    <t>47216153650</t>
+  </si>
+  <si>
+    <t>47216369976</t>
+  </si>
+  <si>
+    <t>47216370166</t>
+  </si>
+  <si>
+    <t>47216370430</t>
+  </si>
+  <si>
+    <t>47216404256</t>
+  </si>
+  <si>
+    <t>47216587462</t>
+  </si>
+  <si>
+    <t>47216893623</t>
+  </si>
+  <si>
+    <t>47217099742</t>
+  </si>
+  <si>
+    <t>47217178951</t>
+  </si>
+  <si>
+    <t>47217245668</t>
+  </si>
+  <si>
+    <t>47217315711</t>
+  </si>
+  <si>
+    <t>47217316055</t>
+  </si>
+  <si>
+    <t>47217316075</t>
+  </si>
+  <si>
+    <t>47217398866</t>
+  </si>
+  <si>
+    <t>47217419418</t>
+  </si>
+  <si>
+    <t>47217472432</t>
+  </si>
+  <si>
+    <t>47225012453</t>
+  </si>
+  <si>
+    <t>47224995931</t>
+  </si>
+  <si>
+    <t>47224995869</t>
+  </si>
+  <si>
+    <t>47224995841</t>
+  </si>
+  <si>
+    <t>47224921837</t>
+  </si>
+  <si>
+    <t>47224910761</t>
+  </si>
+  <si>
+    <t>47224812725</t>
+  </si>
+  <si>
+    <t>47224724116</t>
+  </si>
+  <si>
+    <t>47224449831</t>
+  </si>
+  <si>
+    <t>47224385958</t>
+  </si>
+  <si>
+    <t>47224339105</t>
+  </si>
+  <si>
+    <t>47224218167</t>
+  </si>
+  <si>
+    <t>47224094272</t>
+  </si>
+  <si>
+    <t>47223944381</t>
+  </si>
+  <si>
+    <t>47223926493</t>
+  </si>
+  <si>
+    <t>47223937589</t>
+  </si>
+  <si>
+    <t>47223806908</t>
+  </si>
+  <si>
+    <t>47223791769</t>
+  </si>
+  <si>
+    <t>47223784689</t>
+  </si>
+  <si>
+    <t>47223605378</t>
+  </si>
+  <si>
+    <t>47223539014</t>
+  </si>
+  <si>
+    <t>47223501780</t>
+  </si>
+  <si>
+    <t>47223441666</t>
+  </si>
+  <si>
+    <t>47223329781</t>
+  </si>
+  <si>
+    <t>47223306949</t>
+  </si>
+  <si>
+    <t>47223264413</t>
+  </si>
+  <si>
+    <t>47223227095</t>
+  </si>
+  <si>
+    <t>47223142467</t>
+  </si>
+  <si>
+    <t>47227465619</t>
+  </si>
+  <si>
+    <t>47227511317</t>
+  </si>
+  <si>
+    <t>47227568028</t>
+  </si>
+  <si>
+    <t>47227739706</t>
+  </si>
+  <si>
+    <t>47227803006</t>
+  </si>
+  <si>
+    <t>47227819786</t>
+  </si>
+  <si>
+    <t>47227996068</t>
+  </si>
+  <si>
+    <t>47228062242</t>
+  </si>
+  <si>
+    <t>47228117230</t>
+  </si>
+  <si>
+    <t>47228131808</t>
+  </si>
+  <si>
+    <t>47180115865</t>
+  </si>
+  <si>
+    <t>47190899556</t>
+  </si>
+  <si>
+    <t>47196496777</t>
+  </si>
+  <si>
+    <t>47200046391</t>
+  </si>
+  <si>
+    <t>47202267619</t>
+  </si>
+  <si>
+    <t>47202929264</t>
+  </si>
+  <si>
+    <t>47207877623</t>
+  </si>
+  <si>
+    <t>47208969004</t>
+  </si>
+  <si>
+    <t>47209555131</t>
+  </si>
+  <si>
+    <t>47209881190</t>
+  </si>
+  <si>
+    <t>47211425310</t>
+  </si>
+  <si>
+    <t>47217492403</t>
+  </si>
+  <si>
+    <t>47217605089</t>
+  </si>
+  <si>
+    <t>47217766674</t>
+  </si>
+  <si>
+    <t>47219333416</t>
+  </si>
+  <si>
+    <t>47227198140</t>
+  </si>
+  <si>
+    <t>47227165468</t>
+  </si>
+  <si>
+    <t>47226973929</t>
+  </si>
+  <si>
+    <t>47226944037</t>
+  </si>
+  <si>
+    <t>47226861176</t>
+  </si>
+  <si>
+    <t>47226629647</t>
+  </si>
+  <si>
+    <t>47226505942</t>
+  </si>
+  <si>
+    <t>47226481042</t>
+  </si>
+  <si>
+    <t>47226390176</t>
+  </si>
+  <si>
+    <t>47226334622</t>
+  </si>
+  <si>
+    <t>47226271616</t>
+  </si>
+  <si>
+    <t>47226185518</t>
+  </si>
+  <si>
+    <t>47226052587</t>
+  </si>
+  <si>
+    <t>47225978785</t>
+  </si>
+  <si>
+    <t>47140067708</t>
+  </si>
+  <si>
+    <t>47153770303</t>
+  </si>
+  <si>
+    <t>47180409187</t>
+  </si>
+  <si>
+    <t>47191175009</t>
+  </si>
+  <si>
+    <t>47196819340</t>
+  </si>
+  <si>
+    <t>47201893179</t>
+  </si>
+  <si>
+    <t>47202197613</t>
+  </si>
+  <si>
+    <t>47204335042</t>
+  </si>
+  <si>
+    <t>47204830493</t>
+  </si>
+  <si>
+    <t>47206367276</t>
+  </si>
+  <si>
+    <t>47206658771</t>
+  </si>
+  <si>
+    <t>47206778184</t>
+  </si>
+  <si>
+    <t>47209718838</t>
+  </si>
+  <si>
+    <t>47210435936</t>
+  </si>
+  <si>
+    <t>47210743466</t>
+  </si>
+  <si>
+    <t>47211134045</t>
+  </si>
+  <si>
+    <t>47211280282</t>
+  </si>
+  <si>
+    <t>47211359550</t>
+  </si>
+  <si>
+    <t>47212119783</t>
+  </si>
+  <si>
+    <t>47212223702</t>
+  </si>
+  <si>
+    <t>47212575038</t>
+  </si>
+  <si>
+    <t>47213768154</t>
+  </si>
+  <si>
+    <t>47215673575</t>
+  </si>
+  <si>
+    <t>47216337951</t>
+  </si>
+  <si>
+    <t>47216390259</t>
+  </si>
+  <si>
+    <t>47216573463</t>
+  </si>
+  <si>
+    <t>47216819808</t>
+  </si>
+  <si>
+    <t>47216824485</t>
+  </si>
+  <si>
+    <t>47217099454</t>
+  </si>
+  <si>
+    <t>47217432935</t>
+  </si>
+  <si>
+    <t>47227587380</t>
+  </si>
+  <si>
+    <t>47227283754</t>
+  </si>
+  <si>
+    <t>47226981787</t>
+  </si>
+  <si>
+    <t>47226366370</t>
+  </si>
+  <si>
+    <t>47226232829</t>
+  </si>
+  <si>
+    <t>47226158293</t>
+  </si>
+  <si>
+    <t>47225733864</t>
+  </si>
+  <si>
+    <t>47225533433</t>
+  </si>
+  <si>
+    <t>47225507992</t>
+  </si>
+  <si>
+    <t>47225202231</t>
+  </si>
+  <si>
+    <t>47224541207</t>
+  </si>
+  <si>
+    <t>47224521000</t>
+  </si>
+  <si>
+    <t>47224514293</t>
+  </si>
+  <si>
+    <t>47224510646</t>
+  </si>
+  <si>
+    <t>47224374573</t>
+  </si>
+  <si>
+    <t>47223787897</t>
+  </si>
+  <si>
+    <t>47223715110</t>
+  </si>
+  <si>
+    <t>47223510784</t>
+  </si>
+  <si>
+    <t>47223393631</t>
+  </si>
+  <si>
+    <t>47223223397</t>
+  </si>
+  <si>
+    <t>47222469262</t>
+  </si>
+  <si>
+    <t>47221894737</t>
+  </si>
+  <si>
+    <t>47221161426</t>
+  </si>
+  <si>
+    <t>47220896904</t>
+  </si>
+  <si>
+    <t>47220869938</t>
+  </si>
+  <si>
+    <t>47220869842</t>
+  </si>
+  <si>
+    <t>47220866464</t>
+  </si>
+  <si>
+    <t>47220769008</t>
+  </si>
+  <si>
+    <t>47220708937</t>
+  </si>
+  <si>
+    <t>47220635117</t>
+  </si>
+  <si>
+    <t>47218570264</t>
+  </si>
+  <si>
+    <t>47218690169</t>
+  </si>
+  <si>
+    <t>47219265167</t>
+  </si>
+  <si>
+    <t>47219408092</t>
+  </si>
+  <si>
+    <t>47219661073</t>
+  </si>
+  <si>
+    <t>47219737536</t>
+  </si>
+  <si>
+    <t>47219935724</t>
+  </si>
+  <si>
+    <t>47220060646</t>
+  </si>
+  <si>
+    <t>47220068227</t>
+  </si>
+  <si>
+    <t>47220207177</t>
+  </si>
+  <si>
+    <t>47220307404</t>
+  </si>
+  <si>
+    <t>47220433799</t>
+  </si>
+  <si>
+    <t>47220440695</t>
+  </si>
+  <si>
+    <t>47220481654</t>
+  </si>
+  <si>
+    <t>47220492265</t>
+  </si>
+  <si>
+    <t>47220494193</t>
+  </si>
+  <si>
+    <t>47226432572</t>
+  </si>
+  <si>
+    <t>47223690555</t>
+  </si>
+  <si>
+    <t>47220909508</t>
+  </si>
+  <si>
+    <t>47218616959</t>
+  </si>
+  <si>
+    <t>47211214674</t>
+  </si>
+  <si>
+    <t>47211899785</t>
+  </si>
+  <si>
+    <t>47211134087</t>
+  </si>
+  <si>
+    <t>47210908643</t>
+  </si>
+  <si>
+    <t>47206556535</t>
+  </si>
+  <si>
+    <t>47201981378</t>
+  </si>
+  <si>
+    <t>47186242919</t>
+  </si>
+  <si>
+    <t>47228081882</t>
+  </si>
+  <si>
+    <t>47227947326</t>
+  </si>
+  <si>
+    <t>47149803233</t>
+  </si>
+  <si>
+    <t>47155373224</t>
+  </si>
+  <si>
+    <t>47164889887</t>
+  </si>
+  <si>
+    <t>47172799005</t>
+  </si>
+  <si>
+    <t>47173240428</t>
+  </si>
+  <si>
+    <t>47177418103</t>
+  </si>
+  <si>
+    <t>47178754465</t>
+  </si>
+  <si>
+    <t>47180298171</t>
+  </si>
+  <si>
+    <t>47184934410</t>
+  </si>
+  <si>
+    <t>47184996014</t>
+  </si>
+  <si>
+    <t>47185340434</t>
+  </si>
+  <si>
+    <t>47185651763</t>
+  </si>
+  <si>
+    <t>47186598177</t>
+  </si>
+  <si>
+    <t>47186871948</t>
+  </si>
+  <si>
+    <t>47187268518</t>
+  </si>
+  <si>
+    <t>47189761859</t>
+  </si>
+  <si>
+    <t>47190842207</t>
+  </si>
+  <si>
+    <t>47192124023</t>
+  </si>
+  <si>
+    <t>47195459498</t>
+  </si>
+  <si>
+    <t>47196397875</t>
+  </si>
+  <si>
+    <t>47196497661</t>
+  </si>
+  <si>
+    <t>47197536007</t>
+  </si>
+  <si>
+    <t>47197733159</t>
+  </si>
+  <si>
+    <t>47197781259</t>
+  </si>
+  <si>
+    <t>47198243309</t>
+  </si>
+  <si>
+    <t>47198311882</t>
+  </si>
+  <si>
+    <t>47198399126</t>
+  </si>
+  <si>
+    <t>47199444558</t>
+  </si>
+  <si>
+    <t>47220073880</t>
+  </si>
+  <si>
+    <t>47219967451</t>
+  </si>
+  <si>
+    <t>47219947201</t>
+  </si>
+  <si>
+    <t>47219930768</t>
+  </si>
+  <si>
+    <t>47219915821</t>
+  </si>
+  <si>
+    <t>47219728486</t>
+  </si>
+  <si>
+    <t>47219699691</t>
+  </si>
+  <si>
+    <t>47219687215</t>
+  </si>
+  <si>
+    <t>47219566502</t>
+  </si>
+  <si>
+    <t>47219277281</t>
+  </si>
+  <si>
+    <t>47219262172</t>
+  </si>
+  <si>
+    <t>47219170436</t>
+  </si>
+  <si>
+    <t>47219138260</t>
+  </si>
+  <si>
+    <t>47218780629</t>
+  </si>
+  <si>
+    <t>47218775115</t>
+  </si>
+  <si>
+    <t>47218716043</t>
+  </si>
+  <si>
+    <t>47218711802</t>
+  </si>
+  <si>
+    <t>47218646227</t>
+  </si>
+  <si>
+    <t>47218632934</t>
+  </si>
+  <si>
+    <t>47218630266</t>
+  </si>
+  <si>
+    <t>47218624721</t>
+  </si>
+  <si>
+    <t>47218227660</t>
+  </si>
+  <si>
+    <t>47218160757</t>
+  </si>
+  <si>
+    <t>47217924492</t>
+  </si>
+  <si>
+    <t>47217934997</t>
+  </si>
+  <si>
+    <t>47217879144</t>
+  </si>
+  <si>
+    <t>47217818963</t>
+  </si>
+  <si>
+    <t>47217724931</t>
+  </si>
+  <si>
+    <t>47217518466</t>
+  </si>
+  <si>
+    <t>47200268785</t>
+  </si>
+  <si>
+    <t>47200548426</t>
+  </si>
+  <si>
+    <t>47201242925</t>
+  </si>
+  <si>
+    <t>47201308567</t>
+  </si>
+  <si>
+    <t>47201870464</t>
+  </si>
+  <si>
+    <t>47202309805</t>
+  </si>
+  <si>
+    <t>47202317543</t>
+  </si>
+  <si>
+    <t>47202385863</t>
+  </si>
+  <si>
+    <t>47202551585</t>
+  </si>
+  <si>
+    <t>47202744851</t>
+  </si>
+  <si>
+    <t>47202757094</t>
+  </si>
+  <si>
+    <t>47202795813</t>
+  </si>
+  <si>
+    <t>47202826586</t>
+  </si>
+  <si>
+    <t>47202914523</t>
+  </si>
+  <si>
+    <t>47202923655</t>
+  </si>
+  <si>
+    <t>47202972050</t>
+  </si>
+  <si>
+    <t>47204784973</t>
+  </si>
+  <si>
+    <t>47205059588</t>
+  </si>
+  <si>
+    <t>47205059644</t>
+  </si>
+  <si>
+    <t>47205431179</t>
+  </si>
+  <si>
+    <t>47205699612</t>
+  </si>
+  <si>
+    <t>47205878052</t>
+  </si>
+  <si>
+    <t>47206625824</t>
+  </si>
+  <si>
+    <t>47206716427</t>
+  </si>
+  <si>
+    <t>47207877845</t>
+  </si>
+  <si>
+    <t>47207994354</t>
+  </si>
+  <si>
+    <t>47207995479</t>
+  </si>
+  <si>
+    <t>47208221381</t>
+  </si>
+  <si>
+    <t>47220888288</t>
+  </si>
+  <si>
+    <t>47220875306</t>
+  </si>
+  <si>
+    <t>47220817205</t>
+  </si>
+  <si>
+    <t>47220786918</t>
+  </si>
+  <si>
+    <t>47220750817</t>
+  </si>
+  <si>
+    <t>47220748218</t>
+  </si>
+  <si>
+    <t>47220739225</t>
+  </si>
+  <si>
+    <t>47220726505</t>
+  </si>
+  <si>
+    <t>47220718991</t>
+  </si>
+  <si>
+    <t>47220698167</t>
+  </si>
+  <si>
+    <t>47220694485</t>
+  </si>
+  <si>
+    <t>47220656045</t>
+  </si>
+  <si>
+    <t>47220655939</t>
+  </si>
+  <si>
+    <t>47220644784</t>
+  </si>
+  <si>
+    <t>47220632118</t>
+  </si>
+  <si>
+    <t>47220600701</t>
+  </si>
+  <si>
+    <t>47220564944</t>
+  </si>
+  <si>
+    <t>47220561579</t>
+  </si>
+  <si>
+    <t>47220496418</t>
+  </si>
+  <si>
+    <t>47220484304</t>
+  </si>
+  <si>
+    <t>47220411051</t>
+  </si>
+  <si>
+    <t>47220410369</t>
+  </si>
+  <si>
+    <t>47220355349</t>
+  </si>
+  <si>
+    <t>47220316811</t>
+  </si>
+  <si>
+    <t>47220281668</t>
+  </si>
+  <si>
+    <t>47220221676</t>
+  </si>
+  <si>
+    <t>47220207441</t>
+  </si>
+  <si>
+    <t>47220096704</t>
+  </si>
+  <si>
+    <t>47220096586</t>
+  </si>
+  <si>
+    <t>47208247704</t>
+  </si>
+  <si>
+    <t>47208292291</t>
+  </si>
+  <si>
+    <t>47209550690</t>
+  </si>
+  <si>
+    <t>47209565197</t>
+  </si>
+  <si>
+    <t>47210278993</t>
+  </si>
+  <si>
+    <t>47210510802</t>
+  </si>
+  <si>
+    <t>47210602723</t>
+  </si>
+  <si>
+    <t>47211016518</t>
+  </si>
+  <si>
+    <t>47211168707</t>
+  </si>
+  <si>
+    <t>47211368631</t>
+  </si>
+  <si>
+    <t>47225957708</t>
+  </si>
+  <si>
+    <t>47225941402</t>
+  </si>
+  <si>
+    <t>47225876287</t>
+  </si>
+  <si>
+    <t>47225759771</t>
+  </si>
+  <si>
+    <t>47225713762</t>
+  </si>
+  <si>
+    <t>47225670622</t>
+  </si>
+  <si>
+    <t>47225616628</t>
+  </si>
+  <si>
+    <t>47225418182</t>
+  </si>
+  <si>
+    <t>47225387046</t>
+  </si>
+  <si>
+    <t>47225369644</t>
+  </si>
+  <si>
+    <t>47225275333</t>
+  </si>
+  <si>
+    <t>47225235260</t>
+  </si>
+  <si>
+    <t>47225190858</t>
+  </si>
+  <si>
+    <t>47225185104</t>
+  </si>
+  <si>
+    <t>47225113284</t>
+  </si>
+  <si>
+    <t>47225068841</t>
+  </si>
+  <si>
+    <t>47225065993</t>
+  </si>
+  <si>
+    <t>47225021155</t>
+  </si>
+  <si>
+    <t>47226823824</t>
+  </si>
+  <si>
+    <t>47220750685</t>
+  </si>
+  <si>
+    <t>47220090652</t>
+  </si>
+  <si>
+    <t>47219436997</t>
+  </si>
+  <si>
+    <t>47227256516</t>
+  </si>
+  <si>
+    <t>47227311656</t>
+  </si>
+  <si>
+    <t>47227370507</t>
+  </si>
+  <si>
+    <t>47227381486</t>
+  </si>
+  <si>
+    <t>47227406597</t>
+  </si>
+  <si>
+    <t>47227439906</t>
+  </si>
+  <si>
+    <t>47227446818</t>
+  </si>
+  <si>
+    <t>47227465043</t>
+  </si>
+  <si>
+    <t>47224405026</t>
+  </si>
+  <si>
+    <t>47224441788</t>
+  </si>
+  <si>
+    <t>47225081379</t>
+  </si>
+  <si>
+    <t>47225522103</t>
+  </si>
+  <si>
+    <t>47224637803</t>
+  </si>
+  <si>
+    <t>47220446072</t>
+  </si>
+  <si>
+    <t>47220435526</t>
+  </si>
+  <si>
+    <t>47220581830</t>
+  </si>
+  <si>
+    <t>47224545105</t>
+  </si>
+  <si>
+    <t>47220671250</t>
+  </si>
+  <si>
+    <t>47220844003</t>
+  </si>
+  <si>
+    <t>47182818338</t>
+  </si>
+  <si>
+    <t>47185311766</t>
+  </si>
+  <si>
+    <t>47220764717</t>
+  </si>
+  <si>
+    <t>47178488308</t>
+  </si>
+  <si>
+    <t>47189437633</t>
+  </si>
+  <si>
+    <t>47220880630</t>
+  </si>
+  <si>
+    <t>47220884047</t>
+  </si>
+  <si>
+    <t>47196283814</t>
+  </si>
+  <si>
+    <t>47224826711</t>
+  </si>
+  <si>
+    <t>47193561429</t>
+  </si>
+  <si>
+    <t>47221558973</t>
+  </si>
+  <si>
+    <t>47198441953</t>
+  </si>
+  <si>
+    <t>47198441995</t>
+  </si>
+  <si>
+    <t>47222440195</t>
+  </si>
+  <si>
+    <t>47199967319</t>
+  </si>
+  <si>
+    <t>47222956911</t>
+  </si>
+  <si>
+    <t>47223203939</t>
+  </si>
+  <si>
+    <t>47224131219</t>
+  </si>
+  <si>
+    <t>47209605796</t>
+  </si>
+  <si>
+    <t>47211037393</t>
+  </si>
+  <si>
+    <t>47224787456</t>
+  </si>
+  <si>
+    <t>47224997517</t>
+  </si>
+  <si>
+    <t>47211645576</t>
+  </si>
+  <si>
+    <t>47225271886</t>
+  </si>
+  <si>
+    <t>47225511999</t>
+  </si>
+  <si>
+    <t>47212316132</t>
+  </si>
+  <si>
+    <t>47212398347</t>
+  </si>
+  <si>
+    <t>47216350756</t>
+  </si>
+  <si>
+    <t>47215947098</t>
+  </si>
+  <si>
+    <t>47226723230</t>
+  </si>
+  <si>
+    <t>47216657228</t>
+  </si>
+  <si>
+    <t>47217240002</t>
+  </si>
+  <si>
+    <t>47216950827</t>
+  </si>
+  <si>
+    <t>47227411184</t>
+  </si>
+  <si>
+    <t>47218489185</t>
+  </si>
+  <si>
+    <t>47218780876</t>
+  </si>
+  <si>
+    <t>47218780910</t>
+  </si>
+  <si>
+    <t>47161838791</t>
+  </si>
+  <si>
+    <t>47228063198</t>
+  </si>
+  <si>
+    <t>47228053872</t>
+  </si>
+  <si>
+    <t>47218780920</t>
+  </si>
+  <si>
+    <t>47207599627</t>
+  </si>
+  <si>
+    <t>47220005014</t>
+  </si>
+  <si>
+    <t>47220184381</t>
+  </si>
+  <si>
+    <t>47220184527</t>
+  </si>
+  <si>
+    <t>47184035924</t>
+  </si>
+  <si>
+    <t>47221101494</t>
+  </si>
+  <si>
+    <t>47216515045</t>
+  </si>
+  <si>
+    <t>47236305789</t>
+  </si>
+  <si>
+    <t>47239777293</t>
+  </si>
+  <si>
+    <t>47240531755</t>
+  </si>
+  <si>
+    <t>47242633106</t>
+  </si>
+  <si>
+    <t>47242353221</t>
+  </si>
+  <si>
+    <t>47232824613</t>
+  </si>
+  <si>
+    <t>47223666875</t>
   </si>
 </sst>
 </file>
@@ -222,10 +1623,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,76 +1905,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G517"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
@@ -583,188 +1982,2524 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="2" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G115" s="2"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A449" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A450" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A451" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A452" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A453" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A454" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A455" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A456" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A457" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A460" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A461" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A462" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A463" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A464" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A466" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A467" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A468" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A469" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A470" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A471" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A472" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A473" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A474" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A475" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A476" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A477" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A478" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A479" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A480" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A481" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A482" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A483" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A484" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A485" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A486" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A487" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A488" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A489" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A490" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A491" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A492" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A493" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A494" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A495" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A496" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A497" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A498" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A499" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A500" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A501" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A502" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A503" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A504" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A505" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A506" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A507" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A508" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A509" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A510" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A511" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A512" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A513" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A514" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A515" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A516" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A517" s="2" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
